--- a/outputs/q4/q4_resource_gap.xlsx
+++ b/outputs/q4/q4_resource_gap.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -557,34 +557,34 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>36.247</v>
+        <v>1313.479</v>
       </c>
       <c r="M2" t="n">
-        <v>1313.47819412363</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-008,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -619,34 +619,34 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="M3" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Q2-007,Q2-013</t>
+          <t>Q2-019,Q2-026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -681,34 +681,34 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2072.307384815261</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-025</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -743,34 +743,34 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1993.126</v>
+        <v>2229.758</v>
       </c>
       <c r="M5" t="n">
-        <v>2192.366042252357</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-003,Q2-004,Q2-008,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-015,Q2-016,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -805,34 +805,34 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2102.64</v>
+        <v>4869.153</v>
       </c>
       <c r="M6" t="n">
-        <v>3026.097809356639</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Q2-005,Q2-007,Q2-013,Q2-020</t>
+          <t>Q2-003,Q2-006,Q2-011,Q2-012</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -867,34 +867,34 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3642.85</v>
+        <v>1815.961</v>
       </c>
       <c r="M7" t="n">
-        <v>4530.415759184022</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-018,Q2-025</t>
+          <t>Q2-005,Q2-021,Q2-022,Q2-025</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -942,14 +942,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="M8" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>strict_no_duplication-K2-P003</t>
+          <t>strict_no_duplication-K2-P001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="M9" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -1073,14 +1073,14 @@
         <v>1313.479</v>
       </c>
       <c r="M10" t="n">
-        <v>1993.125811655315</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-003,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1132,17 +1132,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="M11" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Q2-007,Q2-013</t>
+          <t>Q2-019,Q2-026</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1177,34 +1177,34 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K3-G1</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2072.307384815261</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-025</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1256,17 +1256,17 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="M13" t="n">
-        <v>3177.611936577518</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="N13" t="n">
         <v>6</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-015,Q2-016,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1301,16 +1301,16 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2102.64</v>
+        <v>4869.153</v>
       </c>
       <c r="M14" t="n">
-        <v>3026.097809356639</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Q2-005,Q2-007,Q2-013</t>
+          <t>Q2-003,Q2-006,Q2-011,Q2-012</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1363,16 +1363,16 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3642.85</v>
+        <v>4291.262</v>
       </c>
       <c r="M15" t="n">
-        <v>4530.415759184022</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-018,Q2-025</t>
+          <t>Q2-008,Q2-018,Q2-021,Q2-025</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="M16" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="M17" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="N17" t="n">
         <v>3</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.247</v>
+        <v>1313.479</v>
       </c>
       <c r="M18" t="n">
-        <v>1313.47819412363</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-008,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1611,34 +1611,34 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="M19" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Q2-007,Q2-013</t>
+          <t>Q2-019,Q2-026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1673,34 +1673,34 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2072.307384815261</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-025</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1735,34 +1735,34 @@
         <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1993.126</v>
+        <v>2229.758</v>
       </c>
       <c r="M21" t="n">
-        <v>2192.366042252357</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-003,Q2-004,Q2-008,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-015,Q2-016,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1797,34 +1797,34 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2102.64</v>
+        <v>4869.153</v>
       </c>
       <c r="M22" t="n">
-        <v>3026.097809356639</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Q2-005,Q2-007,Q2-013,Q2-020</t>
+          <t>Q2-003,Q2-006,Q2-011,Q2-012</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1859,34 +1859,34 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3642.85</v>
+        <v>1815.961</v>
       </c>
       <c r="M23" t="n">
-        <v>4530.415759184022</v>
+        <v>3216.20214937907</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-018,Q2-025</t>
+          <t>Q2-005,Q2-021,Q2-022,Q2-025</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1934,21 +1934,21 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="M24" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="N24" t="n">
         <v>2</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R01,K2-G2-Q3-R02</t>
+          <t>K2-G1-Q3-R01,K2-G1-Q3-R02</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>replicate_relay-K2-P031</t>
+          <t>replicate_relay-K2-P008</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1996,21 +1996,21 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>K2-G2</t>
+          <t>K2-G1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="M25" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="N25" t="n">
         <v>3</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>K2-G2-Q3-R01,K2-G2-Q3-R02,K2-G2-Q3-R03</t>
+          <t>K2-G1-Q3-R01,K2-G1-Q3-R02,K2-G1-Q3-R03</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>1313.479</v>
       </c>
       <c r="M26" t="n">
-        <v>1993.125811655315</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-003,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2124,17 +2124,17 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>65.366</v>
+        <v>46.776</v>
       </c>
       <c r="M27" t="n">
-        <v>1641.641398980425</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="N27" t="n">
         <v>2</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Q2-007,Q2-013</t>
+          <t>Q2-019,Q2-026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2169,34 +2169,34 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>K3-G2</t>
+          <t>K3-G1</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1626.17</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2072.307384815261</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-025</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2248,17 +2248,17 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2277.287</v>
+        <v>2229.758</v>
       </c>
       <c r="M29" t="n">
-        <v>3177.611936577518</v>
+        <v>3174.895936577519</v>
       </c>
       <c r="N29" t="n">
         <v>6</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-009,Q2-016</t>
+          <t>Q2-009,Q2-014,Q2-015,Q2-016,Q2-020,Q2-024</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2293,16 +2293,16 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2102.64</v>
+        <v>4869.153</v>
       </c>
       <c r="M30" t="n">
-        <v>3026.097809356639</v>
+        <v>5550.5346802819</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Q2-005,Q2-007,Q2-013</t>
+          <t>Q2-003,Q2-006,Q2-011,Q2-012</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2355,16 +2355,16 @@
         <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2372,17 +2372,17 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3642.85</v>
+        <v>4291.262</v>
       </c>
       <c r="M31" t="n">
-        <v>4530.415759184022</v>
+        <v>6060.090759184022</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Q2-017,Q2-018,Q2-025</t>
+          <t>Q2-008,Q2-018,Q2-021,Q2-025</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="M32" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>replicate_relay-K3-P059</t>
+          <t>replicate_relay-K3-P077</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="M33" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
       <c r="N33" t="n">
         <v>3</v>
